--- a/order_generation/PO_excel/EC-5001.xlsx
+++ b/order_generation/PO_excel/EC-5001.xlsx
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -254,13 +254,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -733,7 +736,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="86.25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>宁波品秀美容科技有限公司
 宁波高新区江南路1528号高新科技广场2号楼10楼
@@ -741,7 +744,7 @@
 sales@hair-brushes.com    lucky@jsiu.com</t>
         </is>
       </c>
-      <c r="H1" s="28" t="n"/>
+      <c r="H1" s="26" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -867,28 +870,28 @@
       <c r="H6" s="20" t="n"/>
     </row>
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>EC-5001</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>粉色指甲钳五件套，含指甲剪、指甲锉等工具，附收纳盒</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="29" t="n">
         <v>1.8</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>纸盒包装</t>
         </is>
@@ -896,23 +899,23 @@
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="19" t="n"/>
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">

--- a/order_generation/PO_excel/EC-5001.xlsx
+++ b/order_generation/PO_excel/EC-5001.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年10月09日</t>
+          <t>2025年10月21日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年11月23日</t>
+          <t>2025年12月05日</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>

--- a/order_generation/PO_excel/EC-5001.xlsx
+++ b/order_generation/PO_excel/EC-5001.xlsx
@@ -364,6 +364,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -721,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15.140625" customWidth="1" style="7" min="1" max="1"/>
@@ -1000,7 +1003,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年12月05日</t>
+          <t>45天</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1237,16 +1240,9 @@
     <row r="34" ht="21" customFormat="1" customHeight="1" s="6">
       <c r="H34" s="14" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="H38" s="14" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="12" t="n"/>
@@ -1347,7 +1343,6 @@
       <c r="A67" s="10" t="n"/>
       <c r="B67" s="12" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="17.25" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
@@ -1379,26 +1374,9 @@
       </c>
       <c r="F70" s="13" t="n"/>
     </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="H80" s="14" t="n"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
